--- a/data/trans_orig/P15E_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>22825</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23676</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>31388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>47441</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>47441</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>47441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17911</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>20530</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14445</t>
+          <t>15493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28295</t>
+          <t>31317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38067</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>51474</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40306</t>
+          <t>44879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52475</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7703</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35127</t>
+          <t>37813</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>45323</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>17206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24402</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50613</t>
+          <t>55272</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44458</t>
+          <t>48615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56894</t>
+          <t>61589</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>70474</t>
+          <t>77555</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62743</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78283</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,57%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34109</t>
+          <t>38104</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>89004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>116798</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
